--- a/data/trans_dic/IQ2605_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IQ2605_R2-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>41,92%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56,28%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>74,12%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>40,5%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>45,83%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>55,34%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>79,18%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>46,55%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>41,92%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>56,28%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,12%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>42,28%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,3; 57,46</t>
+          <t>31,46; 53,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,7; 66,51</t>
+          <t>45,81; 67,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,27; 87,01</t>
+          <t>64,13; 82,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,92; 69,57</t>
+          <t>21,8; 60,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,62; 53,21</t>
+          <t>36,18; 56,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,23; 66,65</t>
+          <t>44,61; 66,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,73; 82,39</t>
+          <t>68,99; 86,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,88; 64,39</t>
+          <t>23,44; 67,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35,51; 51,39</t>
+          <t>36,19; 51,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,49; 63,28</t>
+          <t>47,96; 62,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68,69; 81,98</t>
+          <t>68,95; 81,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,86; 58,53</t>
+          <t>29,52; 57,2</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43,68%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>73,43%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>87,46%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>69,62%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>47,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>80,55%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>87,79%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>63,8%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>43,68%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>73,43%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>87,46%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>65,24%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,68; 55,38</t>
+          <t>36,18; 51,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,45; 86,08</t>
+          <t>66,58; 80,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,07; 92,58</t>
+          <t>81,68; 91,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44,3; 80,09</t>
+          <t>51,87; 85,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,73; 51,5</t>
+          <t>39,45; 54,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,4; 79,81</t>
+          <t>73,58; 86,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,19; 91,83</t>
+          <t>81,37; 92,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,47; 86,59</t>
+          <t>39,67; 74,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40,26; 51,56</t>
+          <t>39,48; 51,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71,84; 81,46</t>
+          <t>71,98; 81,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82,84; 91,04</t>
+          <t>83,72; 91,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,38; 80,16</t>
+          <t>51,48; 77,01</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>39,88%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>82,86%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>63,82%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>72,98%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>51,05%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>88,66%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>53,06%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>69,95%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>39,88%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,86%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>63,82%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,38; 60,99</t>
+          <t>30,07; 49,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,39; 94,16</t>
+          <t>74,25; 89,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,78; 64,9</t>
+          <t>53,36; 73,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,46; 84,49</t>
+          <t>52,58; 87,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,63; 48,89</t>
+          <t>41,53; 61,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74,8; 90,04</t>
+          <t>80,3; 94,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53,62; 72,6</t>
+          <t>41,78; 63,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52,63; 91,16</t>
+          <t>52,85; 84,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,45; 52,46</t>
+          <t>38,84; 52,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80,3; 90,32</t>
+          <t>80,6; 90,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,65; 66,66</t>
+          <t>51,72; 66,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59,89; 83,24</t>
+          <t>57,57; 81,93</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>53,9%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>81,26%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>89,77%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>89,77%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>54,51%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>85,38%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>82,53%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>36,58%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>53,9%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>81,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>89,77%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,69%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,46; 64,39</t>
+          <t>44,35; 63,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,12; 91,31</t>
+          <t>73,64; 88,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74,39; 89,47</t>
+          <t>82,39; 94,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,92; 60,2</t>
+          <t>63,04; 100,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,61; 63,49</t>
+          <t>45,14; 64,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,45; 87,35</t>
+          <t>77,27; 91,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,68; 94,4</t>
+          <t>74,06; 88,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59,23; 100,0</t>
+          <t>16,51; 62,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,38; 60,96</t>
+          <t>47,48; 60,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77,95; 88,2</t>
+          <t>77,26; 87,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80,69; 90,53</t>
+          <t>81,59; 90,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38,08; 75,66</t>
+          <t>37,36; 75,67</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>64,74%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>61,9%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>92,7%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>90,72%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>53,14%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>54,86%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>88,76%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>87,13%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>64,74%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>61,9%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>92,7%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,32%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,3; 66,47</t>
+          <t>51,51; 75,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,24; 66,84</t>
+          <t>48,91; 72,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78,95; 95,61</t>
+          <t>83,92; 97,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67,37; 97,05</t>
+          <t>71,6; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,2; 76,23</t>
+          <t>40,27; 65,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,35; 73,15</t>
+          <t>40,54; 67,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,37; 97,37</t>
+          <t>78,19; 95,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>68,52; 100,0</t>
+          <t>67,31; 97,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50,67; 67,47</t>
+          <t>49,27; 67,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49,25; 66,78</t>
+          <t>49,1; 66,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84,49; 95,08</t>
+          <t>84,19; 95,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>78,48; 96,94</t>
+          <t>77,76; 96,57</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>46,6%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82,48%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>72,46%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>82,57%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>41,59%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>80,72%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>66,38%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>83,6%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>46,6%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>82,48%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>72,46%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,27%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,36; 51,72</t>
+          <t>36,07; 56,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69,77; 88,45</t>
+          <t>72,6; 89,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55,23; 76,54</t>
+          <t>60,84; 81,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56,6; 100,0</t>
+          <t>63,03; 94,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,85; 57,25</t>
+          <t>29,85; 51,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,96; 89,09</t>
+          <t>71,15; 88,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61,3; 81,59</t>
+          <t>53,97; 76,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>66,51; 94,11</t>
+          <t>55,98; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37,35; 51,41</t>
+          <t>37,33; 51,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74,35; 86,82</t>
+          <t>75,08; 87,43</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62,89; 77,33</t>
+          <t>61,92; 76,65</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>68,7; 93,87</t>
+          <t>69,76; 92,45</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>53,16%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>71,92%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>66,63%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>74,45%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>52,01%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>67,89%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>64,89%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>78,19%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>53,16%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>71,92%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>66,63%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,57%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>44,93; 58,92</t>
+          <t>45,97; 60,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>60,93; 74,24</t>
+          <t>65,51; 77,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58,19; 71,34</t>
+          <t>60,09; 73,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62,12; 88,65</t>
+          <t>60,67; 86,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,8; 60,16</t>
+          <t>45,09; 60,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,58; 77,82</t>
+          <t>60,74; 74,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,98; 73,04</t>
+          <t>57,69; 71,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>60,32; 85,77</t>
+          <t>61,96; 88,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>47,71; 57,79</t>
+          <t>47,73; 57,46</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64,83; 74,47</t>
+          <t>64,85; 74,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61,74; 70,69</t>
+          <t>61,09; 69,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,17; 83,62</t>
+          <t>64,94; 84,15</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>66,48%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>72,51%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>86,2%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>90,25%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>68,21%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>71,63%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>82,51%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>97,37%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>66,48%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>72,51%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>86,2%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,87%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>61,86; 73,75</t>
+          <t>60,19; 72,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>66,01; 77,3</t>
+          <t>66,37; 77,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77,2; 86,85</t>
+          <t>81,15; 90,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84,47; 100,0</t>
+          <t>79,08; 96,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,58; 72,22</t>
+          <t>61,53; 74,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,08; 78,32</t>
+          <t>65,8; 76,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,18; 90,04</t>
+          <t>77,05; 86,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>79,77; 96,31</t>
+          <t>78,5; 100,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>62,96; 71,38</t>
+          <t>63,31; 71,74</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68,34; 76,42</t>
+          <t>68,18; 76,01</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81,07; 87,51</t>
+          <t>80,79; 87,09</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>86,37; 97,48</t>
+          <t>85,23; 97,14</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>52,84%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>73,23%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>79,17%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>76,34%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>53,95%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>73,6%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>76,01%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>71,91%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>52,84%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>73,23%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>79,17%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>50,7; 56,96</t>
+          <t>49,8; 55,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>70,72; 76,62</t>
+          <t>70,59; 75,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73,37; 78,56</t>
+          <t>76,43; 81,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65,58; 77,76</t>
+          <t>70,69; 81,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>49,62; 55,78</t>
+          <t>51,06; 57,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>70,52; 75,94</t>
+          <t>70,61; 76,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>76,32; 81,49</t>
+          <t>73,26; 78,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>70,27; 82,03</t>
+          <t>64,42; 77,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>51,23; 55,57</t>
+          <t>51,22; 55,46</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71,3; 75,34</t>
+          <t>71,27; 75,38</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>75,76; 79,45</t>
+          <t>75,71; 79,35</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>70,5; 78,57</t>
+          <t>69,65; 78,26</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23205</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34564</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47778</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7114</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>22633</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>31238</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>43909</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6266</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>23205</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34564</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>47778</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15078</t>
+          <t>12654</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17435; 28380</t>
+          <t>17415; 29401</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25231; 37545</t>
+          <t>28134; 41646</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38967; 48247</t>
+          <t>41343; 53059</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3354; 9365</t>
+          <t>3830; 10578</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17503; 29453</t>
+          <t>17870; 27956</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27777; 40930</t>
+          <t>25182; 37312</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41080; 53109</t>
+          <t>38255; 48175</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5122; 13257</t>
+          <t>2899; 8407</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37194; 53830</t>
+          <t>37905; 53981</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57154; 74585</t>
+          <t>56530; 74209</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82363; 98303</t>
+          <t>82680; 98302</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10169; 19930</t>
+          <t>8836; 17122</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>138</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>46663</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>76379</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>95330</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>20131</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>45701</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>81098</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>89724</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14652</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>46663</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76379</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95330</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23048</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37700</t>
+          <t>32069</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37617; 53856</t>
+          <t>38648; 55142</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73944; 86665</t>
+          <t>69254; 83488</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82851; 94617</t>
+          <t>89028; 100190</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10175; 18392</t>
+          <t>14998; 24675</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38169; 55009</t>
+          <t>38364; 53432</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68025; 83012</t>
+          <t>74077; 86990</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88501; 100096</t>
+          <t>83161; 94857</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17054; 28142</t>
+          <t>8030; 15151</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82149; 105214</t>
+          <t>80574; 105505</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>147053; 166739</t>
+          <t>147335; 166493</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>174957; 192282</t>
+          <t>176811; 192581</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30160; 44459</t>
+          <t>25307; 37855</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>27540</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>56740</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>43763</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10320</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>33749</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>57997</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>33217</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13455</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>27540</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>56740</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43763</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>13518</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25504</t>
+          <t>23837</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27357; 40321</t>
+          <t>20764; 33851</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>51928; 61590</t>
+          <t>50844; 60985</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26781; 40633</t>
+          <t>36593; 50339</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9899; 16253</t>
+          <t>7435; 12309</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>21842; 33760</t>
+          <t>27455; 40663</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51222; 61659</t>
+          <t>52523; 61667</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36772; 49787</t>
+          <t>26160; 39760</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8454; 14645</t>
+          <t>10217; 16246</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>51972; 70902</t>
+          <t>52492; 70536</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>107516; 120934</t>
+          <t>107923; 121107</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67751; 87448</t>
+          <t>67844; 86881</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21141; 29383</t>
+          <t>19272; 27426</t>
         </is>
       </c>
     </row>
@@ -2702,32 +2702,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>91</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>42322</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>66822</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>72877</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9496</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>39783</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>63669</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>62635</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5361</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>42322</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>66822</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>72877</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9548</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>15141</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33177; 46990</t>
+          <t>34818; 49788</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58256; 68095</t>
+          <t>60554; 72425</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56453; 67901</t>
+          <t>66887; 76560</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2480; 8824</t>
+          <t>6669; 10578</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35021; 49846</t>
+          <t>32946; 46972</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59578; 71830</t>
+          <t>57623; 67990</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67122; 76641</t>
+          <t>56206; 67407</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6420; 10839</t>
+          <t>2513; 9491</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71778; 92351</t>
+          <t>71930; 92267</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>122236; 138309</t>
+          <t>121153; 137835</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>126749; 142195</t>
+          <t>128157; 141947</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9709; 19291</t>
+          <t>9637; 19520</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>28595</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28524</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>42260</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10019</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>21545</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>24084</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>38026</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8957</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>28595</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28524</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>42260</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18843</t>
+          <t>19394</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16743; 26947</t>
+          <t>22752; 33551</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18543; 29344</t>
+          <t>22534; 33620</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33821; 40961</t>
+          <t>38257; 44419</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6926; 9977</t>
+          <t>7908; 11044</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23056; 33672</t>
+          <t>16326; 26598</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22740; 33705</t>
+          <t>17796; 29455</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38464; 44389</t>
+          <t>33495; 40936</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7289; 10637</t>
+          <t>7181; 10415</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42927; 57156</t>
+          <t>41737; 57208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44314; 60083</t>
+          <t>44179; 59848</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74711; 84078</t>
+          <t>74452; 84143</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16416; 20277</t>
+          <t>16885; 20968</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>27545</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>46717</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>41836</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>13091</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>23315</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>42562</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>35596</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7422</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>27545</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>46717</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>41836</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15335</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22757</t>
+          <t>20610</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17579; 28991</t>
+          <t>21324; 33357</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36790; 46638</t>
+          <t>41121; 50600</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29616; 41043</t>
+          <t>35127; 47216</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5025; 8878</t>
+          <t>9993; 14928</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21781; 33844</t>
+          <t>16734; 29061</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>41328; 50461</t>
+          <t>37514; 46544</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35395; 47112</t>
+          <t>28942; 40802</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12227; 17301</t>
+          <t>4981; 8898</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>43021; 59209</t>
+          <t>42992; 59631</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>81316; 94951</t>
+          <t>82118; 95626</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70039; 86118</t>
+          <t>68959; 85357</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18728; 25591</t>
+          <t>17267; 22883</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>135</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>70475</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>99176</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>95167</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>30371</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>66552</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>91169</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>88750</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>22082</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>70475</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99176</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>95167</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>32393</t>
+          <t>20856</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>54475</t>
+          <t>51228</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>57495; 75398</t>
+          <t>60938; 80323</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>81822; 99691</t>
+          <t>90333; 106785</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>79590; 97577</t>
+          <t>85831; 104663</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17544; 25036</t>
+          <t>24749; 35461</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>60713; 79757</t>
+          <t>57702; 77019</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>90431; 107301</t>
+          <t>81569; 100121</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85666; 104328</t>
+          <t>78914; 97491</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>26342; 37456</t>
+          <t>16726; 23937</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>124290; 150563</t>
+          <t>124347; 149694</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>176465; 202705</t>
+          <t>176514; 201806</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>172624; 197662</t>
+          <t>170830; 195268</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>46861; 60133</t>
+          <t>44020; 57042</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>172</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>212</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>107057</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>121837</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>144765</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>35624</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>105302</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>114488</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>134233</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>24709</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>107057</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>121837</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>144765</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>35378</t>
+          <t>25005</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>60087</t>
+          <t>60629</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>95505; 113865</t>
+          <t>96931; 116189</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>105505; 123556</t>
+          <t>111509; 130154</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>125605; 141290</t>
+          <t>136291; 151392</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21436; 25376</t>
+          <t>31215; 38138</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>97555; 116306</t>
+          <t>95000; 114412</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>112706; 131603</t>
+          <t>105182; 122978</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>136337; 151215</t>
+          <t>125350; 140786</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>31180; 37643</t>
+          <t>20263; 25814</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>198596; 225149</t>
+          <t>199702; 226294</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>224058; 250537</t>
+          <t>223521; 249219</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>268052; 289348</t>
+          <t>267108; 287937</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>55678; 62839</t>
+          <t>55647; 63422</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>538</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>733</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>163</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>758</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>837</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>373402</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>530759</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>583776</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>136167</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>358579</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>506305</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>526091</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>102905</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>373402</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>530759</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>583776</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>146448</t>
+          <t>99396</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>249353</t>
+          <t>235563</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>336981; 378576</t>
+          <t>351905; 393254</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>486435; 527029</t>
+          <t>511646; 548841</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>507772; 543676</t>
+          <t>563535; 600903</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>93844; 111272</t>
+          <t>126085; 145254</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>350621; 394190</t>
+          <t>339361; 379085</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>511119; 550397</t>
+          <t>485730; 525483</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>562734; 600860</t>
+          <t>507027; 543833</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>134765; 157301</t>
+          <t>89886; 107975</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>702468; 762083</t>
+          <t>702365; 760534</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1007259; 1064264</t>
+          <t>1006721; 1064836</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1082965; 1135614</t>
+          <t>1082220; 1134290</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>236071; 263118</t>
+          <t>221415; 248795</t>
         </is>
       </c>
     </row>
